--- a/studies/flume-mooring/test-matrix/HSFP_1-50_Wave_Test_Matrix_9-26-2026_FloatSim.xlsx
+++ b/studies/flume-mooring/test-matrix/HSFP_1-50_Wave_Test_Matrix_9-26-2026_FloatSim.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ea38421b3c6b4430/Documents/buoy/HSP_code/studies/flume-mooring/test-matrix/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D0E610E973AF237DDBE63DF8D8363B4FCC28777C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="11_D1E610E973AF237DDBE63D0EF8B33F4A64AE65A6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3840" yWindow="3920" windowWidth="19200" windowHeight="11170" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5240" yWindow="4110" windowWidth="19200" windowHeight="11170" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Summary" sheetId="1" r:id="rId1"/>
@@ -865,7 +865,7 @@
     <t>In waves the heave RAO peaks later than the decay period: ~2.65-2.70 s model on the flume BEM (≈ 18.5-19 s FS after the mesh correction).</t>
   </si>
   <si>
-    <t>2. Moored slow modes (MOORING-SPEC rev C.1 §5) and the decay record they need</t>
+    <t>2. Moored slow modes (MOORING-SPEC rev D §5) and the decay record they need</t>
   </si>
   <si>
     <t>Cord set</t>
@@ -6418,20 +6418,20 @@
         <v>264</v>
       </c>
       <c r="D16" s="26">
-        <v>2.6059999999999999</v>
+        <v>2.5990000000000002</v>
       </c>
       <c r="E16" s="26">
-        <v>2.5630000000000002</v>
+        <v>2.5569999999999999</v>
       </c>
       <c r="F16" s="27">
         <f>E16*SQRT(Inputs!$B$4)</f>
-        <v>18.123146801811213</v>
+        <v>18.08072039494002</v>
       </c>
       <c r="G16" s="28">
-        <v>0.106</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="H16" s="26">
-        <v>0.59099999999999997</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="I16" s="23" t="s">
         <v>267</v>
@@ -6448,20 +6448,20 @@
         <v>266</v>
       </c>
       <c r="D17" s="26">
-        <v>2.6059999999999999</v>
+        <v>2.5979999999999999</v>
       </c>
       <c r="E17" s="26">
-        <v>2.5630000000000002</v>
+        <v>2.556</v>
       </c>
       <c r="F17" s="27">
         <f>E17*SQRT(Inputs!$B$4)</f>
-        <v>18.123146801811213</v>
+        <v>18.073649327128155</v>
       </c>
       <c r="G17" s="28">
-        <v>0.106</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="H17" s="26">
-        <v>0.59099999999999997</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="I17" s="23" t="s">
         <v>267</v>
@@ -6478,20 +6478,20 @@
         <v>270</v>
       </c>
       <c r="D18" s="26">
-        <v>2.605</v>
+        <v>2.5979999999999999</v>
       </c>
       <c r="E18" s="26">
-        <v>2.5630000000000002</v>
+        <v>2.5550000000000002</v>
       </c>
       <c r="F18" s="27">
         <f>E18*SQRT(Inputs!$B$4)</f>
-        <v>18.123146801811213</v>
+        <v>18.066578259316291</v>
       </c>
       <c r="G18" s="28">
-        <v>0.106</v>
+        <v>0.10299999999999999</v>
       </c>
       <c r="H18" s="26">
-        <v>0.59099999999999997</v>
+        <v>0.57399999999999995</v>
       </c>
       <c r="I18" s="23" t="s">
         <v>267</v>
@@ -6508,7 +6508,7 @@
         <v>264</v>
       </c>
       <c r="D19" s="26">
-        <v>2.9239999999999999</v>
+        <v>2.9260000000000002</v>
       </c>
       <c r="E19" s="26">
         <v>2.8639999999999999</v>
@@ -6518,10 +6518,10 @@
         <v>20.25153821318272</v>
       </c>
       <c r="G19" s="28">
-        <v>3.2000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="H19" s="26">
-        <v>0.16700000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="I19" s="23" t="s">
         <v>267</v>
@@ -6538,7 +6538,7 @@
         <v>266</v>
       </c>
       <c r="D20" s="26">
-        <v>2.9020000000000001</v>
+        <v>2.9039999999999999</v>
       </c>
       <c r="E20" s="26">
         <v>2.8420000000000001</v>
@@ -6548,10 +6548,10 @@
         <v>20.095974721321681</v>
       </c>
       <c r="G20" s="28">
-        <v>3.2000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="H20" s="26">
-        <v>0.16700000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="I20" s="23" t="s">
         <v>267</v>
@@ -6568,20 +6568,20 @@
         <v>270</v>
       </c>
       <c r="D21" s="26">
-        <v>2.7879999999999998</v>
+        <v>2.7989999999999999</v>
       </c>
       <c r="E21" s="26">
-        <v>2.7280000000000002</v>
+        <v>2.7370000000000001</v>
       </c>
       <c r="F21" s="27">
         <f>E21*SQRT(Inputs!$B$4)</f>
-        <v>19.28987299076902</v>
+        <v>19.353512601075806</v>
       </c>
       <c r="G21" s="28">
-        <v>3.2000000000000001E-2</v>
+        <v>0.03</v>
       </c>
       <c r="H21" s="26">
-        <v>0.16700000000000001</v>
+        <v>0.161</v>
       </c>
       <c r="I21" s="23" t="s">
         <v>267</v>
@@ -6763,24 +6763,24 @@
         <v>286</v>
       </c>
       <c r="C30" s="23">
-        <v>23.02</v>
+        <v>22.92</v>
       </c>
       <c r="D30" s="23">
-        <v>58.98</v>
+        <v>60.76</v>
       </c>
       <c r="E30" s="23">
-        <v>33.4</v>
+        <v>32.72</v>
       </c>
       <c r="F30" s="29">
         <f>C30*SQRT(Inputs!$B$4)</f>
-        <v>162.77598102914325</v>
+        <v>162.0688742479567</v>
       </c>
       <c r="G30" s="29">
         <f>D30*SQRT(Inputs!$B$4)</f>
-        <v>417.05157954382571</v>
+        <v>429.63808024894627</v>
       </c>
       <c r="H30" s="23">
-        <v>4.9000000000000004</v>
+        <v>5.0999999999999996</v>
       </c>
       <c r="I30" s="23"/>
     </row>
@@ -6792,24 +6792,24 @@
         <v>287</v>
       </c>
       <c r="C31" s="23">
-        <v>9.59</v>
+        <v>9.91</v>
       </c>
       <c r="D31" s="23">
-        <v>28.28</v>
+        <v>31.05</v>
       </c>
       <c r="E31" s="23">
-        <v>18.079999999999998</v>
+        <v>17.09</v>
       </c>
       <c r="F31" s="29">
         <f>C31*SQRT(Inputs!$B$4)</f>
-        <v>67.811540315789912</v>
+        <v>70.07428201558686</v>
       </c>
       <c r="G31" s="29">
         <f>D31*SQRT(Inputs!$B$4)</f>
-        <v>199.96979771955566</v>
+        <v>219.55665555842302</v>
       </c>
       <c r="H31" s="23">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="I31" s="23"/>
     </row>
